--- a/dados/tradutor_gempack.xlsx
+++ b/dados/tradutor_gempack.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\Documents\dev_2026\gd_impacta_mg\dados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\desenvolvimentos\apps\gd_impacta_mg\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EBD23E-DFAE-4789-B101-ADF0A8F4CF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E6A052F-7F79-4136-A779-F2749ACE7D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{98DCC10F-1E1E-46D0-8590-C8CA17A0E6A3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{98DCC10F-1E1E-46D0-8590-C8CA17A0E6A3}"/>
   </bookViews>
   <sheets>
     <sheet name="scn" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="318">
   <si>
     <t>Agricultura, inclusive o apoio à agricultura e a pós-colheita</t>
   </si>
@@ -1381,14 +1381,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F252F04-A08C-4FA9-905C-4954B0E10AD9}">
   <dimension ref="A1:C71"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="73.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>245</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>164</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>165</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>166</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>167</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>168</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>169</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>170</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>171</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>172</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>173</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>174</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>175</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>176</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>177</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>178</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>179</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>180</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>181</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>182</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>183</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>184</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>185</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>186</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>187</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>188</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>189</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>190</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>191</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>192</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>193</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>194</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>195</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>196</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>197</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>198</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>199</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>200</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>201</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>202</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>203</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>204</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>204</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>205</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>206</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>207</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>208</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>86</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>209</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>210</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>211</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>212</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>213</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>214</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>215</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>216</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>217</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>218</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>219</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>220</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>221</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>222</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>223</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>224</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>225</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>226</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>227</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>228</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>229</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>237</v>
       </c>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C70" s="3"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>248</v>
       </c>
@@ -1965,13 +1965,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C227EC9-34AC-47C0-95B9-D13F88A59410}">
   <dimension ref="A1:B67"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>246</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>27</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>244</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>34</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>36</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>40</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>42</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>44</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>46</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>48</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>50</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>52</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>54</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>56</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>58</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>60</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>238</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>63</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>65</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>67</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>69</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>71</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>73</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>75</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>77</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>241</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>79</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>81</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>243</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>85</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>87</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>89</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>91</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>93</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>242</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>96</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>98</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>100</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>240</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>103</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>105</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>239</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>108</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>110</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>112</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>113</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>114</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>115</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>116</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>118</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>120</v>
       </c>
@@ -2515,9 +2515,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{492F478D-B099-4A7B-86C0-0E09192BA6B8}">
   <dimension ref="A1:B71"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>250</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2685,7 +2685,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2949,7 +2949,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3092,749 +3092,547 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE36E45-731C-4997-9B28-65103B874937}">
-  <dimension ref="A1:C67"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B67"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>317</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>251</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>252</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>253</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>254</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>255</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>256</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>257</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>258</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>259</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>260</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>261</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>262</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>263</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>264</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>265</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>266</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>267</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>268</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>269</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>270</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>271</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>272</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>273</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>274</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>275</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>276</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>277</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>278</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>279</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>280</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>281</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>282</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>283</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>284</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>285</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>286</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>287</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>288</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>289</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>290</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>291</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>292</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>293</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>294</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>295</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>296</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>297</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>298</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>299</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>300</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>301</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>302</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>303</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>304</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>305</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>306</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>307</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>308</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>309</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>310</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>311</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>312</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>313</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>314</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>315</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>316</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/dados/tradutor_gempack.xlsx
+++ b/dados/tradutor_gempack.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\desenvolvimentos\apps\gd_impacta_mg\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E6A052F-7F79-4136-A779-F2749ACE7D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21BC476-8FA7-4FAB-99E2-372FA3AA739C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{98DCC10F-1E1E-46D0-8590-C8CA17A0E6A3}"/>
+    <workbookView xWindow="19515" yWindow="4650" windowWidth="21780" windowHeight="20985" activeTab="3" xr2:uid="{98DCC10F-1E1E-46D0-8590-C8CA17A0E6A3}"/>
   </bookViews>
   <sheets>
     <sheet name="scn" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="319">
   <si>
     <t>Agricultura, inclusive o apoio à agricultura e a pós-colheita</t>
   </si>
@@ -993,6 +993,9 @@
   </si>
   <si>
     <t>resultado</t>
+  </si>
+  <si>
+    <t>São João del Rei</t>
   </si>
 </sst>
 </file>
@@ -3544,7 +3547,7 @@
         <v>305</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>103</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
